--- a/reports/二级子公司C_利润表_2025-11.xlsx
+++ b/reports/二级子公司C_利润表_2025-11.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>85956644</v>
+        <v>87047456</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>83496427</v>
+        <v>82609788</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>953063999</v>
+        <v>952736770</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>385867</v>
+        <v>389719</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>4451873</v>
+        <v>4450404</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>337463</v>
+        <v>341435</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>3893487</v>
+        <v>3896052</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>289415</v>
+        <v>292736</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3335948</v>
+        <v>3341060</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>270531</v>
+        <v>273008</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3112813</v>
+        <v>3119467</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>145248</v>
+        <v>146007</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1667519</v>
+        <v>1671465</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>116490</v>
+        <v>116537</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1334250</v>
+        <v>1337155</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>84411630</v>
+        <v>85488014</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>81951413</v>
+        <v>81050346</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>78058627</v>
+        <v>77191519</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>890677168</v>
+        <v>890468578</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1170768</v>
+        <v>1157037</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>13366127</v>
+        <v>13350390</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>779644</v>
+        <v>771618</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>8913545</v>
+        <v>8896491</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2918004</v>
+        <v>2897433</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>33429962</v>
+        <v>33352675</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>388125</v>
+        <v>387135</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4456947</v>
+        <v>4446676</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>290370</v>
+        <v>291073</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3341772</v>
+        <v>3335448</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>482929</v>
+        <v>486303</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>5567242</v>
+        <v>5560861</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>578728</v>
+        <v>584707</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>6677363</v>
+        <v>6676041</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2410482</v>
+        <v>2439057</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>27808953</v>
+        <v>27830804</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>49735</v>
+        <v>50296</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>549401</v>
+        <v>550436</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1169826</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>13369636</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>778489</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>8914577</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>58230268</v>
+        <v>61960601</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>51870566</v>
+        <v>51401832</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>50699630</v>
+        <v>50244138</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>578688407</v>
+        <v>579049432</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1170936</v>
+        <v>1157694</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>13361020</v>
+        <v>13356128</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1928363</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>22249261</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>617371</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>7116863</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>386418</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4446923</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>464709</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>5336040</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>349405</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>4002669</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>233495</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2669357</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>194942</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2225493</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>867801</v>
+        <v>878128</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>10010641</v>
+        <v>10019750</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>675516</v>
+        <v>682978</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>7783244</v>
+        <v>7796678</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>580019</v>
+        <v>584800</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>6670113</v>
+        <v>6685041</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4360299</v>
+        <v>4377734</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>50026961</v>
+        <v>50144836</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>200288</v>
+        <v>194099</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2197809</v>
+        <v>2228503</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>351295</v>
+        <v>349305</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3847883</v>
+        <v>3853498</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>402125</v>
+        <v>349305</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4399970</v>
+        <v>3853498</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>50299</v>
+        <v>49722</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>550295</v>
+        <v>549934</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>178921</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1978712</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>337672</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3891864</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>119541</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1318290</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>89857</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>988716</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>150138</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1648234</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>486587</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>5561472</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>80404</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>879893</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>60356</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>660282</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>100578</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1100996</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>70322</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>770942</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>50131</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>550729</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>40007</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>440525</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>29931</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>330282</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>26181362</v>
+        <v>24732042</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>30626002</v>
+        <v>27947138</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>192841</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2224659</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>49739</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>549389</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>80145</v>
+        <v>79715</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>881150</v>
+        <v>878847</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>26101217</v>
+        <v>24845168</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2791394</v>
+        <v>2803512</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>30821501</v>
+        <v>30768484</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>23309823</v>
+        <v>22041656</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>23309823</v>
+        <v>22041656</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>23309823</v>
+        <v>22041656</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>23309823</v>
+        <v>22041656</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>23309823</v>
+        <v>22041656</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
